--- a/output/pdf_financials_xlsx/EGLX.xlsx
+++ b/output/pdf_financials_xlsx/EGLX.xlsx
@@ -3280,10 +3280,10 @@
         <v>2.130681</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.776988</v>
+        <v>0.115913</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>9.439323999999999</v>
+        <v>24.844052</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>25.485361</v>
@@ -3295,10 +3295,10 @@
         <v>35.877189</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>17.596195</v>
+        <v>19.419363</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>17.774059</v>
+        <v>20.33529</v>
       </c>
     </row>
     <row r="93">
@@ -5912,7 +5912,11 @@
           <t>Warrants reserve 18</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -7138,7 +7142,11 @@
           <t>Warrants reserve 12, 17</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -10280,7 +10288,11 @@
           <t>Warrants reserve 17</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -11476,7 +11488,11 @@
           <t>Warrants reserve 13, 14</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/EGLX.xlsx
+++ b/output/pdf_financials_xlsx/EGLX.xlsx
@@ -771,22 +771,22 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.677276</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.051529</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.036252</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.064316</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004787</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00599</v>
       </c>
     </row>
     <row r="13">
@@ -1268,22 +1268,22 @@
         <v>-0.384105</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-79.542142</v>
+        <v>-78.86486600000001</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-52.986087</v>
+        <v>-52.934558</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-78.882069</v>
+        <v>-78.845817</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-127.849414</v>
+        <v>-127.785098</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-96.66715000000001</v>
+        <v>-96.662363</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-44.118781</v>
+        <v>-44.112791</v>
       </c>
     </row>
     <row r="28">
@@ -1330,22 +1330,22 @@
         <v>0.174031</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-76.608268</v>
+        <v>-75.930992</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-43.467616</v>
+        <v>-43.416087</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-62.174225</v>
+        <v>-62.137973</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-117.417032</v>
+        <v>-117.352716</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-94.432838</v>
+        <v>-94.428051</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-42.569608</v>
+        <v>-42.563618</v>
       </c>
     </row>
     <row r="30">
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-651.3795043536959</v>
+        <v>-645.6208086318366</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-25.97185877517501</v>
+        <v>-25.94107024720913</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-30.65247254701005</v>
+        <v>-30.63459997304915</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-65.89867902248182</v>
+        <v>-65.86258256042842</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-226.6507602280792</v>
+        <v>-226.6392708223578</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-132.8878184233097</v>
+        <v>-132.8691196832989</v>
       </c>
     </row>
     <row r="31">
@@ -1463,28 +1463,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.362215</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>4.155054</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>13.211722</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>22.654262</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>7.415516</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>6.851966</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>4.765373</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>3.262528</v>
       </c>
     </row>
     <row r="35">
@@ -1525,28 +1525,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.362215</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>4.155054</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>13.211722</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>22.654262</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>7.415516</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>6.851966</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>4.765373</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>3.262528</v>
       </c>
     </row>
     <row r="37">
@@ -1897,28 +1897,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.246185</v>
+        <v>0.88397</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.860179</v>
+        <v>1.705125</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>14.628973</v>
+        <v>1.417251</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>25.287154</v>
+        <v>2.632892</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>9.924612</v>
+        <v>2.509096</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>8.703360999999999</v>
+        <v>1.851395</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.78854</v>
+        <v>2.023167</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>4.090857</v>
+        <v>0.828329</v>
       </c>
     </row>
     <row r="49">
@@ -4253,22 +4253,22 @@
         <v>-0.01016</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.087159</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>-23.77347</v>
+        <v>-24.620546</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>-2.588238</v>
+        <v>-3.549149</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>-4.129561</v>
+        <v>-5.128932</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>-6.373678</v>
+        <v>-6.836967</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>-2.268758</v>
+        <v>-2.308117</v>
       </c>
     </row>
     <row r="125">
@@ -4284,22 +4284,22 @@
         <v>-0.01016</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.087159</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>-23.77347</v>
+        <v>-24.620546</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>-2.588238</v>
+        <v>-3.549149</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>-4.129561</v>
+        <v>-5.128932</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>-6.373678</v>
+        <v>-6.836967</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>-2.268758</v>
+        <v>-2.308117</v>
       </c>
     </row>
     <row r="126">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
@@ -14262,7 +14262,11 @@
           <t>Lease payments 11</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -16346,7 +16350,11 @@
           <t>Lease payments 10</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -19586,7 +19594,11 @@
           <t>Lease payments 12</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -21228,7 +21240,11 @@
           <t>Lease payments 11</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -25036,7 +25052,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -28844,7 +28860,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">

--- a/output/pdf_financials_xlsx/EGLX.xlsx
+++ b/output/pdf_financials_xlsx/EGLX.xlsx
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.025997</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -12944,7 +12944,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/EGLX.xlsx
+++ b/output/pdf_financials_xlsx/EGLX.xlsx
@@ -926,7 +926,7 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.995715</v>
+        <v>-0.995715</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0.939465</v>
@@ -1062,11 +1062,15 @@
       <c r="G20" s="3" t="n">
         <v>-117.673608</v>
       </c>
-      <c r="H20" s="3" t="n">
-        <v>-95.983</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>-44.118781</v>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1094,10 +1098,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>-6.126169</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-34.438172</v>
       </c>
     </row>
     <row r="22">
@@ -1652,25 +1656,25 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.68901</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>3.683102</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>5.906625</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.611452</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.68813</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.822451</v>
       </c>
     </row>
     <row r="41">
@@ -1683,25 +1687,25 @@
         <v>1.236075</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.907023</v>
+        <v>7.596033</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>33.978921</v>
+        <v>37.662023</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>37.919042</v>
+        <v>43.825667</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>31.502732</v>
+        <v>32.114184</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>12.351539</v>
+        <v>13.039669</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>4.806842</v>
+        <v>5.629293</v>
       </c>
     </row>
     <row r="42">
@@ -1900,25 +1904,25 @@
         <v>0.88397</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.705125</v>
+        <v>1.700125</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.417251</v>
+        <v>0.728241</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.632892</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.509096</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.851395</v>
+        <v>1.239943</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.023167</v>
+        <v>1.335037</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.828329</v>
+        <v>0.005878</v>
       </c>
     </row>
     <row r="49">
@@ -2505,25 +2509,25 @@
         <v>0.021542</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0135</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.485339</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>9.14387</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>9.419191</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>11.853432</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>5.922254</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>3.828823</v>
       </c>
     </row>
     <row r="68">
@@ -3814,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.06149</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -3826,13 +3830,13 @@
         <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.191722</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>-0.161878</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>-0.097784</v>
       </c>
     </row>
     <row r="111">
@@ -4012,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.027488</v>
       </c>
       <c r="H116" s="3" t="n">
         <v>0</v>
@@ -12620,7 +12624,11 @@
           <t>Accretion 11,13,14</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -12674,7 +12682,11 @@
           <t>Deferred tax recovery 19</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -15354,7 +15366,11 @@
           <t>Accretion 10,12,13</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -15408,7 +15424,11 @@
           <t>Deferred tax recovery 18</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -16128,7 +16148,11 @@
           <t>Acquisition of intangible assets 7</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -16854,7 +16878,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -17680,7 +17708,11 @@
           <t>Acquisition of intangible assets 9</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -18302,7 +18334,11 @@
           <t>Deferred tax recovery 22</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -21710,7 +21746,11 @@
           <t>Accretion expense 10</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -21822,7 +21862,11 @@
           <t>Deferred income tax recovery 16</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -25312,7 +25356,11 @@
           <t>Net loss from discontinued operations 5</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -32894,7 +32942,11 @@
           <t>Deferred income tax recovery 19</t>
         </is>
       </c>
-      <c r="D509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E509" t="inlineStr">
         <is>
           <t>-</t>
